--- a/AAII_Financials/Quarterly/NGLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NGLD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
   <si>
     <t>NGLD</t>
   </si>
@@ -656,140 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,8 +883,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,16 +1110,17 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
@@ -1115,23 +1128,23 @@
       <c r="G12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
+      <c r="K12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L12" s="3">
         <v>0</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
+      <c r="M12" s="3">
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
@@ -1139,17 +1152,17 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>4</v>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S12" s="3">
-        <v>0</v>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T12" s="3">
         <v>0</v>
@@ -1161,23 +1174,23 @@
         <v>0</v>
       </c>
       <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>4</v>
+      <c r="Y12" s="3">
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3">
-        <v>0</v>
-      </c>
       <c r="AC12" s="3">
         <v>0</v>
       </c>
@@ -1188,10 +1201,13 @@
         <v>0</v>
       </c>
       <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,37 +1522,38 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E17" s="3">
         <v>700</v>
       </c>
       <c r="F17" s="3">
+        <v>700</v>
+      </c>
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>400</v>
       </c>
       <c r="I17" s="3">
         <v>400</v>
       </c>
       <c r="J17" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K17" s="3">
         <v>100</v>
       </c>
       <c r="L17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
@@ -1548,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T17" s="3">
         <v>100</v>
@@ -1560,11 +1586,11 @@
         <v>100</v>
       </c>
       <c r="W17" s="3">
+        <v>100</v>
+      </c>
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
       <c r="Y17" s="3">
         <v>0</v>
       </c>
@@ -1572,11 +1598,11 @@
         <v>0</v>
       </c>
       <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3">
         <v>700</v>
       </c>
-      <c r="AB17" s="3">
-        <v>0</v>
-      </c>
       <c r="AC17" s="3">
         <v>0</v>
       </c>
@@ -1584,13 +1610,16 @@
         <v>0</v>
       </c>
       <c r="AE17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1601,25 +1630,25 @@
         <v>-700</v>
       </c>
       <c r="F18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-400</v>
       </c>
       <c r="I18" s="3">
         <v>-400</v>
       </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
@@ -1640,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3">
         <v>-100</v>
@@ -1652,11 +1681,11 @@
         <v>-100</v>
       </c>
       <c r="W18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
         <v>0</v>
       </c>
@@ -1664,11 +1693,11 @@
         <v>0</v>
       </c>
       <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
       <c r="AC18" s="3">
         <v>0</v>
       </c>
@@ -1676,13 +1705,16 @@
         <v>0</v>
       </c>
       <c r="AE18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1747,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1727,76 +1760,76 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-400</v>
       </c>
       <c r="I20" s="3">
         <v>-400</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>300</v>
       </c>
       <c r="Q20" s="3">
         <v>300</v>
       </c>
       <c r="R20" s="3">
+        <v>300</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>2300</v>
       </c>
       <c r="AB20" s="3">
         <v>2300</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -1807,8 +1840,11 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1818,12 +1854,12 @@
       <c r="E21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,37 +1935,40 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
@@ -1946,8 +1985,8 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1967,14 +2006,14 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1991,100 +2030,106 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-800</v>
       </c>
       <c r="E23" s="3">
         <v>-700</v>
       </c>
       <c r="F23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-800</v>
       </c>
       <c r="I23" s="3">
         <v>-800</v>
       </c>
       <c r="J23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>300</v>
       </c>
       <c r="Q23" s="3">
         <v>300</v>
       </c>
       <c r="R23" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="S23" s="3">
         <v>-200</v>
       </c>
       <c r="T23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U23" s="3">
         <v>-1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2300</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
       <c r="AD23" s="3">
         <v>0</v>
       </c>
       <c r="AE23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2158,11 +2203,11 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2175,8 +2220,11 @@
       <c r="AF24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-800</v>
       </c>
       <c r="E26" s="3">
         <v>-700</v>
       </c>
       <c r="F26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-800</v>
       </c>
       <c r="I26" s="3">
         <v>-800</v>
       </c>
       <c r="J26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
-      </c>
-      <c r="P26" s="3">
-        <v>300</v>
       </c>
       <c r="Q26" s="3">
         <v>300</v>
       </c>
       <c r="R26" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="S26" s="3">
         <v>-200</v>
       </c>
       <c r="T26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2300</v>
       </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
       <c r="AD26" s="3">
         <v>0</v>
       </c>
       <c r="AE26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-800</v>
       </c>
       <c r="E27" s="3">
         <v>-700</v>
       </c>
       <c r="F27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-800</v>
       </c>
       <c r="I27" s="3">
         <v>-800</v>
       </c>
       <c r="J27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
-      </c>
-      <c r="P27" s="3">
-        <v>300</v>
       </c>
       <c r="Q27" s="3">
         <v>300</v>
       </c>
       <c r="R27" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="S27" s="3">
         <v>-200</v>
       </c>
       <c r="T27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U27" s="3">
         <v>-1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2300</v>
       </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
       <c r="AD27" s="3">
         <v>0</v>
       </c>
       <c r="AE27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2885,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2831,76 +2900,76 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>400</v>
       </c>
       <c r="I32" s="3">
         <v>400</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-300</v>
       </c>
       <c r="Q32" s="3">
         <v>-300</v>
       </c>
       <c r="R32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>400</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-2300</v>
       </c>
       <c r="AB32" s="3">
         <v>-2300</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -2911,100 +2980,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-800</v>
       </c>
       <c r="E33" s="3">
         <v>-700</v>
       </c>
       <c r="F33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-800</v>
       </c>
       <c r="I33" s="3">
         <v>-800</v>
       </c>
       <c r="J33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
-      </c>
-      <c r="P33" s="3">
-        <v>300</v>
       </c>
       <c r="Q33" s="3">
         <v>300</v>
       </c>
       <c r="R33" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="S33" s="3">
         <v>-200</v>
       </c>
       <c r="T33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2300</v>
       </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
       <c r="AD33" s="3">
         <v>0</v>
       </c>
       <c r="AE33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-800</v>
       </c>
       <c r="E35" s="3">
         <v>-700</v>
       </c>
       <c r="F35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-800</v>
       </c>
       <c r="I35" s="3">
         <v>-800</v>
       </c>
       <c r="J35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
-      </c>
-      <c r="P35" s="3">
-        <v>300</v>
       </c>
       <c r="Q35" s="3">
         <v>300</v>
       </c>
       <c r="R35" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="S35" s="3">
         <v>-200</v>
       </c>
       <c r="T35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2300</v>
       </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
       <c r="AD35" s="3">
         <v>0</v>
       </c>
       <c r="AE35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,28 +3437,29 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4700</v>
+        <v>9700</v>
       </c>
       <c r="E41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1400</v>
       </c>
       <c r="J41" s="3">
         <v>1400</v>
@@ -3382,10 +3468,10 @@
         <v>1400</v>
       </c>
       <c r="L41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M41" s="3">
         <v>1000</v>
-      </c>
-      <c r="M41" s="3">
-        <v>900</v>
       </c>
       <c r="N41" s="3">
         <v>900</v>
@@ -3397,13 +3483,13 @@
         <v>900</v>
       </c>
       <c r="Q41" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="R41" s="3">
         <v>500</v>
       </c>
       <c r="S41" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T41" s="3">
         <v>400</v>
@@ -3415,7 +3501,7 @@
         <v>400</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
@@ -3439,13 +3525,16 @@
         <v>0</v>
       </c>
       <c r="AE41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3625,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,7 +3827,7 @@
         <v>500</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3738,11 +3836,11 @@
         <v>0</v>
       </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
         <v>0</v>
       </c>
@@ -3812,40 +3910,43 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E46" s="3">
         <v>10500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1500</v>
-      </c>
-      <c r="J46" s="3">
-        <v>1400</v>
       </c>
       <c r="K46" s="3">
         <v>1400</v>
       </c>
       <c r="L46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M46" s="3">
         <v>1000</v>
-      </c>
-      <c r="M46" s="3">
-        <v>900</v>
       </c>
       <c r="N46" s="3">
         <v>900</v>
@@ -3857,26 +3958,26 @@
         <v>900</v>
       </c>
       <c r="Q46" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="R46" s="3">
         <v>500</v>
       </c>
       <c r="S46" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T46" s="3">
         <v>400</v>
       </c>
       <c r="U46" s="3">
+        <v>400</v>
+      </c>
+      <c r="V46" s="3">
         <v>500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
-      </c>
       <c r="X46" s="3">
         <v>0</v>
       </c>
@@ -3899,13 +4000,16 @@
         <v>0</v>
       </c>
       <c r="AE46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3919,73 +4023,73 @@
         <v>800</v>
       </c>
       <c r="G47" s="3">
+        <v>800</v>
+      </c>
+      <c r="H47" s="3">
         <v>900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>800</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>1000</v>
       </c>
       <c r="Z47" s="3">
         <v>1000</v>
       </c>
       <c r="AA47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB47" s="3">
         <v>1400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2400</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>100</v>
       </c>
       <c r="AD47" s="3">
         <v>100</v>
@@ -3996,8 +4100,11 @@
       <c r="AF47" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4088,8 +4195,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,88 +4670,91 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E54" s="3">
         <v>11300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1500</v>
       </c>
       <c r="M54" s="3">
         <v>1500</v>
       </c>
       <c r="N54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O54" s="3">
         <v>1800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2400</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>100</v>
       </c>
       <c r="AD54" s="3">
         <v>100</v>
@@ -4638,10 +4763,13 @@
         <v>100</v>
       </c>
       <c r="AF54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4735,7 +4865,7 @@
         <v>800</v>
       </c>
       <c r="K57" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="L57" s="3">
         <v>400</v>
@@ -4750,19 +4880,19 @@
         <v>400</v>
       </c>
       <c r="P57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
       </c>
       <c r="R57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
       </c>
       <c r="T57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
@@ -4774,20 +4904,20 @@
         <v>300</v>
       </c>
       <c r="X57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y57" s="3">
         <v>200</v>
       </c>
       <c r="Z57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
       <c r="AC57" s="3">
         <v>0</v>
       </c>
@@ -4800,8 +4930,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4814,24 +4947,24 @@
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4848,25 +4981,25 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>1100</v>
       </c>
       <c r="T58" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="U58" s="3">
         <v>1000</v>
       </c>
       <c r="V58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
-      </c>
-      <c r="X58" s="3">
-        <v>600</v>
       </c>
       <c r="Y58" s="3">
         <v>600</v>
@@ -4878,10 +5011,10 @@
         <v>600</v>
       </c>
       <c r="AB58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC58" s="3">
         <v>200</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>100</v>
       </c>
       <c r="AD58" s="3">
         <v>100</v>
@@ -4892,8 +5025,11 @@
       <c r="AF58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4919,10 +5055,10 @@
         <v>500</v>
       </c>
       <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>1000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1100</v>
       </c>
       <c r="M59" s="3">
         <v>1100</v>
@@ -4940,7 +5076,7 @@
         <v>1100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -4984,13 +5120,16 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>1300</v>
       </c>
       <c r="E60" s="3">
         <v>1300</v>
@@ -5002,25 +5141,25 @@
         <v>1300</v>
       </c>
       <c r="H60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I60" s="3">
         <v>2400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1800</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1500</v>
       </c>
       <c r="M60" s="3">
         <v>1500</v>
       </c>
       <c r="N60" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="O60" s="3">
         <v>1400</v>
@@ -5041,16 +5180,16 @@
         <v>1400</v>
       </c>
       <c r="U60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1100</v>
-      </c>
-      <c r="X60" s="3">
-        <v>800</v>
       </c>
       <c r="Y60" s="3">
         <v>800</v>
@@ -5062,10 +5201,10 @@
         <v>800</v>
       </c>
       <c r="AB60" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC60" s="3">
         <v>200</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>100</v>
       </c>
       <c r="AD60" s="3">
         <v>100</v>
@@ -5076,8 +5215,11 @@
       <c r="AF60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,8 +5310,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5245,8 +5390,8 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
+      <c r="AB62" s="3">
+        <v>0</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5690,11 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5554,25 +5711,25 @@
         <v>1300</v>
       </c>
       <c r="H66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I66" s="3">
         <v>2400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1500</v>
       </c>
       <c r="M66" s="3">
         <v>1500</v>
       </c>
       <c r="N66" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="O66" s="3">
         <v>1400</v>
@@ -5593,16 +5750,16 @@
         <v>1400</v>
       </c>
       <c r="U66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V66" s="3">
         <v>1300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1100</v>
-      </c>
-      <c r="X66" s="3">
-        <v>800</v>
       </c>
       <c r="Y66" s="3">
         <v>800</v>
@@ -5614,10 +5771,10 @@
         <v>800</v>
       </c>
       <c r="AB66" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC66" s="3">
         <v>200</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>100</v>
       </c>
       <c r="AD66" s="3">
         <v>100</v>
@@ -5628,8 +5785,11 @@
       <c r="AF66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-300</v>
       </c>
       <c r="Z72" s="3">
         <v>-300</v>
       </c>
       <c r="AA72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB72" s="3">
         <v>700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1800</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>-500</v>
       </c>
       <c r="AD72" s="3">
         <v>-500</v>
       </c>
       <c r="AE72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="AF72" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,89 +6580,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E76" s="3">
         <v>10000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>100</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
       <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
         <v>400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>400</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
       <c r="R76" s="3">
+        <v>0</v>
+      </c>
+      <c r="S76" s="3">
         <v>-200</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
+        <v>0</v>
+      </c>
+      <c r="U76" s="3">
         <v>200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2300</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
-      </c>
       <c r="AD76" s="3">
         <v>0</v>
       </c>
@@ -6488,10 +6673,13 @@
         <v>0</v>
       </c>
       <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-800</v>
       </c>
       <c r="E81" s="3">
         <v>-700</v>
       </c>
       <c r="F81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-800</v>
       </c>
       <c r="I81" s="3">
         <v>-800</v>
       </c>
       <c r="J81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
-      </c>
-      <c r="P81" s="3">
-        <v>300</v>
       </c>
       <c r="Q81" s="3">
         <v>300</v>
       </c>
       <c r="R81" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="S81" s="3">
         <v>-200</v>
       </c>
       <c r="T81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2300</v>
       </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
       <c r="AD81" s="3">
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,16 +7570,19 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-100</v>
       </c>
       <c r="F89" s="3">
         <v>-100</v>
@@ -7384,11 +7600,11 @@
         <v>-100</v>
       </c>
       <c r="K89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
@@ -7432,11 +7648,11 @@
         <v>0</v>
       </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
         <v>0</v>
       </c>
@@ -7444,13 +7660,16 @@
         <v>0</v>
       </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7551,20 +7771,20 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>-100</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
+      <c r="AC91" s="3">
+        <v>-100</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>4</v>
@@ -7575,8 +7795,11 @@
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,13 +7985,16 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7780,17 +8009,17 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
@@ -7801,17 +8030,17 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -7819,11 +8048,11 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>500</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
@@ -7833,14 +8062,14 @@
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA94" s="3">
-        <v>-100</v>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
+      <c r="AC94" s="3">
+        <v>-100</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>4</v>
@@ -7851,8 +8080,11 @@
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,26 +8495,29 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>9600</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -8280,11 +8525,11 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8294,17 +8539,17 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -8328,13 +8573,13 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB100" s="3">
         <v>100</v>
       </c>
       <c r="AC100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -8343,15 +8588,18 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -8395,8 +8643,8 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
@@ -8413,8 +8661,8 @@
       <c r="X101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -8437,41 +8685,44 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-8700</v>
+        <v>-200</v>
       </c>
       <c r="E102" s="3">
-        <v>-100</v>
+        <v>9200</v>
       </c>
       <c r="F102" s="3">
         <v>-100</v>
       </c>
       <c r="G102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -8479,29 +8730,29 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
@@ -8524,9 +8775,12 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NGLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NGLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>NGLD</t>
   </si>
@@ -656,143 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -886,8 +890,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,19 +1124,20 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
+      <c r="F12" s="3">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>4</v>
@@ -1131,23 +1145,23 @@
       <c r="H12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
+      <c r="L12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>4</v>
+      <c r="N12" s="3">
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>4</v>
@@ -1155,17 +1169,17 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T12" s="3">
-        <v>0</v>
+      <c r="T12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -1177,23 +1191,23 @@
         <v>0</v>
       </c>
       <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>4</v>
+      <c r="Z12" s="3">
+        <v>0</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AC12" s="3">
-        <v>0</v>
-      </c>
       <c r="AD12" s="3">
         <v>0</v>
       </c>
@@ -1204,10 +1218,13 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,40 +1549,41 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
         <v>900</v>
-      </c>
-      <c r="E17" s="3">
-        <v>700</v>
       </c>
       <c r="F17" s="3">
         <v>700</v>
       </c>
       <c r="G17" s="3">
+        <v>700</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>400</v>
       </c>
       <c r="J17" s="3">
         <v>400</v>
       </c>
       <c r="K17" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L17" s="3">
         <v>100</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" s="3">
         <v>0</v>
@@ -1577,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U17" s="3">
         <v>100</v>
@@ -1589,11 +1616,11 @@
         <v>100</v>
       </c>
       <c r="X17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
       <c r="Z17" s="3">
         <v>0</v>
       </c>
@@ -1601,11 +1628,11 @@
         <v>0</v>
       </c>
       <c r="AB17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3">
         <v>700</v>
       </c>
-      <c r="AC17" s="3">
-        <v>0</v>
-      </c>
       <c r="AD17" s="3">
         <v>0</v>
       </c>
@@ -1613,13 +1640,16 @@
         <v>0</v>
       </c>
       <c r="AF17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1627,31 +1657,31 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-700</v>
+        <v>-900</v>
       </c>
       <c r="F18" s="3">
         <v>-700</v>
       </c>
       <c r="G18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-400</v>
       </c>
       <c r="J18" s="3">
         <v>-400</v>
       </c>
       <c r="K18" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="L18" s="3">
         <v>-100</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N18" s="3">
         <v>0</v>
@@ -1672,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3">
         <v>-100</v>
@@ -1684,11 +1714,11 @@
         <v>-100</v>
       </c>
       <c r="X18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
         <v>0</v>
       </c>
@@ -1696,11 +1726,11 @@
         <v>0</v>
       </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
       <c r="AD18" s="3">
         <v>0</v>
       </c>
@@ -1708,13 +1738,16 @@
         <v>0</v>
       </c>
       <c r="AF18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1757,82 +1791,82 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-400</v>
       </c>
       <c r="J20" s="3">
         <v>-400</v>
       </c>
       <c r="K20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>300</v>
       </c>
       <c r="R20" s="3">
         <v>300</v>
       </c>
       <c r="S20" s="3">
+        <v>300</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>2300</v>
       </c>
       <c r="AC20" s="3">
         <v>2300</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
@@ -1843,8 +1877,11 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1857,12 +1894,12 @@
       <c r="F21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3">
         <v>-500</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1938,40 +1975,43 @@
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
@@ -1988,8 +2028,8 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -2009,14 +2049,14 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2033,8 +2073,11 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2042,94 +2085,97 @@
         <v>-800</v>
       </c>
       <c r="E23" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F23" s="3">
         <v>-700</v>
       </c>
       <c r="G23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-800</v>
       </c>
       <c r="J23" s="3">
         <v>-800</v>
       </c>
       <c r="K23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>300</v>
       </c>
       <c r="R23" s="3">
         <v>300</v>
       </c>
       <c r="S23" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="T23" s="3">
         <v>-200</v>
       </c>
       <c r="U23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V23" s="3">
         <v>-1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
       <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2300</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
         <v>0</v>
       </c>
       <c r="AF23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2206,11 +2252,11 @@
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,8 +2367,11 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2327,94 +2379,97 @@
         <v>-800</v>
       </c>
       <c r="E26" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F26" s="3">
         <v>-700</v>
       </c>
       <c r="G26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-800</v>
       </c>
       <c r="J26" s="3">
         <v>-800</v>
       </c>
       <c r="K26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>300</v>
       </c>
       <c r="R26" s="3">
         <v>300</v>
       </c>
       <c r="S26" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="T26" s="3">
         <v>-200</v>
       </c>
       <c r="U26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V26" s="3">
         <v>-1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
       <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2300</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
         <v>0</v>
       </c>
       <c r="AF26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2422,94 +2477,97 @@
         <v>-800</v>
       </c>
       <c r="E27" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F27" s="3">
         <v>-700</v>
       </c>
       <c r="G27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-800</v>
       </c>
       <c r="J27" s="3">
         <v>-800</v>
       </c>
       <c r="K27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>300</v>
       </c>
       <c r="R27" s="3">
         <v>300</v>
       </c>
       <c r="S27" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="T27" s="3">
         <v>-200</v>
       </c>
       <c r="U27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V27" s="3">
         <v>-1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2300</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
         <v>0</v>
       </c>
       <c r="AF27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2897,82 +2967,82 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>400</v>
       </c>
       <c r="J32" s="3">
         <v>400</v>
       </c>
       <c r="K32" s="3">
+        <v>400</v>
+      </c>
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-300</v>
       </c>
       <c r="R32" s="3">
         <v>-300</v>
       </c>
       <c r="S32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>400</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-2300</v>
       </c>
       <c r="AC32" s="3">
         <v>-2300</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
@@ -2983,8 +3053,11 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2992,94 +3065,97 @@
         <v>-800</v>
       </c>
       <c r="E33" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F33" s="3">
         <v>-700</v>
       </c>
       <c r="G33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-800</v>
       </c>
       <c r="J33" s="3">
         <v>-800</v>
       </c>
       <c r="K33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>300</v>
       </c>
       <c r="R33" s="3">
         <v>300</v>
       </c>
       <c r="S33" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="T33" s="3">
         <v>-200</v>
       </c>
       <c r="U33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V33" s="3">
         <v>-1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
       <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2300</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
         <v>0</v>
       </c>
       <c r="AF33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,8 +3249,11 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3182,194 +3261,200 @@
         <v>-800</v>
       </c>
       <c r="E35" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F35" s="3">
         <v>-700</v>
       </c>
       <c r="G35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-800</v>
       </c>
       <c r="J35" s="3">
         <v>-800</v>
       </c>
       <c r="K35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>300</v>
       </c>
       <c r="R35" s="3">
         <v>300</v>
       </c>
       <c r="S35" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="T35" s="3">
         <v>-200</v>
       </c>
       <c r="U35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V35" s="3">
         <v>-1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
       <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2300</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
         <v>0</v>
       </c>
       <c r="AF35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,31 +3524,32 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E41" s="3">
         <v>9700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>1400</v>
       </c>
       <c r="K41" s="3">
         <v>1400</v>
@@ -3471,10 +3558,10 @@
         <v>1400</v>
       </c>
       <c r="M41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N41" s="3">
         <v>1000</v>
-      </c>
-      <c r="N41" s="3">
-        <v>900</v>
       </c>
       <c r="O41" s="3">
         <v>900</v>
@@ -3486,13 +3573,13 @@
         <v>900</v>
       </c>
       <c r="R41" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="S41" s="3">
         <v>500</v>
       </c>
       <c r="T41" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="U41" s="3">
         <v>400</v>
@@ -3504,7 +3591,7 @@
         <v>400</v>
       </c>
       <c r="X41" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
@@ -3528,13 +3615,16 @@
         <v>0</v>
       </c>
       <c r="AF41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,19 +3914,22 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
         <v>500</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -3839,11 +3938,11 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
@@ -3913,43 +4012,46 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E46" s="3">
         <v>10300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1500</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1400</v>
       </c>
       <c r="L46" s="3">
         <v>1400</v>
       </c>
       <c r="M46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N46" s="3">
         <v>1000</v>
-      </c>
-      <c r="N46" s="3">
-        <v>900</v>
       </c>
       <c r="O46" s="3">
         <v>900</v>
@@ -3961,26 +4063,26 @@
         <v>900</v>
       </c>
       <c r="R46" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="S46" s="3">
         <v>500</v>
       </c>
       <c r="T46" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="U46" s="3">
         <v>400</v>
       </c>
       <c r="V46" s="3">
+        <v>400</v>
+      </c>
+      <c r="W46" s="3">
         <v>500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>400</v>
       </c>
-      <c r="X46" s="3">
-        <v>0</v>
-      </c>
       <c r="Y46" s="3">
         <v>0</v>
       </c>
@@ -4003,18 +4105,21 @@
         <v>0</v>
       </c>
       <c r="AF46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E47" s="3">
         <v>800</v>
@@ -4026,73 +4131,73 @@
         <v>800</v>
       </c>
       <c r="H47" s="3">
+        <v>800</v>
+      </c>
+      <c r="I47" s="3">
         <v>900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>800</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>1000</v>
       </c>
       <c r="AA47" s="3">
         <v>1000</v>
       </c>
       <c r="AB47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2400</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>100</v>
       </c>
       <c r="AE47" s="3">
         <v>100</v>
@@ -4103,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4198,8 +4306,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,91 +4796,94 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E54" s="3">
         <v>11100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2000</v>
-      </c>
-      <c r="M54" s="3">
-        <v>1500</v>
       </c>
       <c r="N54" s="3">
         <v>1500</v>
       </c>
       <c r="O54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P54" s="3">
         <v>1800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2400</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>100</v>
       </c>
       <c r="AE54" s="3">
         <v>100</v>
@@ -4766,10 +4892,13 @@
         <v>100</v>
       </c>
       <c r="AG54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4868,7 +4999,7 @@
         <v>800</v>
       </c>
       <c r="L57" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="M57" s="3">
         <v>400</v>
@@ -4883,19 +5014,19 @@
         <v>400</v>
       </c>
       <c r="Q57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R57" s="3">
         <v>300</v>
       </c>
       <c r="S57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T57" s="3">
         <v>400</v>
       </c>
       <c r="U57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
@@ -4907,20 +5038,20 @@
         <v>300</v>
       </c>
       <c r="Y57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z57" s="3">
         <v>200</v>
       </c>
       <c r="AA57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB57" s="3">
         <v>100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
         <v>0</v>
       </c>
@@ -4933,8 +5064,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4950,24 +5084,24 @@
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4984,25 +5118,25 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>1100</v>
       </c>
       <c r="U58" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="V58" s="3">
         <v>1000</v>
       </c>
       <c r="W58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X58" s="3">
         <v>900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>800</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>600</v>
       </c>
       <c r="Z58" s="3">
         <v>600</v>
@@ -5014,10 +5148,10 @@
         <v>600</v>
       </c>
       <c r="AC58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD58" s="3">
         <v>200</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>100</v>
       </c>
       <c r="AE58" s="3">
         <v>100</v>
@@ -5028,8 +5162,11 @@
       <c r="AG58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5058,10 +5195,10 @@
         <v>500</v>
       </c>
       <c r="L59" s="3">
+        <v>500</v>
+      </c>
+      <c r="M59" s="3">
         <v>1000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1100</v>
       </c>
       <c r="N59" s="3">
         <v>1100</v>
@@ -5079,7 +5216,7 @@
         <v>1100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -5123,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5144,25 +5284,25 @@
         <v>1300</v>
       </c>
       <c r="I60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J60" s="3">
         <v>2400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1800</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1500</v>
       </c>
       <c r="N60" s="3">
         <v>1500</v>
       </c>
       <c r="O60" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="P60" s="3">
         <v>1400</v>
@@ -5183,16 +5323,16 @@
         <v>1400</v>
       </c>
       <c r="V60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W60" s="3">
         <v>1300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>800</v>
       </c>
       <c r="Z60" s="3">
         <v>800</v>
@@ -5204,10 +5344,10 @@
         <v>800</v>
       </c>
       <c r="AC60" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD60" s="3">
         <v>200</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>100</v>
       </c>
       <c r="AE60" s="3">
         <v>100</v>
@@ -5218,8 +5358,11 @@
       <c r="AG60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5313,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5393,8 +5539,8 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
+      <c r="AC62" s="3">
+        <v>0</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,8 +5848,11 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5714,25 +5872,25 @@
         <v>1300</v>
       </c>
       <c r="I66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J66" s="3">
         <v>2400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>1500</v>
       </c>
       <c r="N66" s="3">
         <v>1500</v>
       </c>
       <c r="O66" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="P66" s="3">
         <v>1400</v>
@@ -5753,16 +5911,16 @@
         <v>1400</v>
       </c>
       <c r="V66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W66" s="3">
         <v>1300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>800</v>
       </c>
       <c r="Z66" s="3">
         <v>800</v>
@@ -5774,10 +5932,10 @@
         <v>800</v>
       </c>
       <c r="AC66" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD66" s="3">
         <v>200</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>100</v>
       </c>
       <c r="AE66" s="3">
         <v>100</v>
@@ -5788,8 +5946,11 @@
       <c r="AG66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z72" s="3">
-        <v>-300</v>
       </c>
       <c r="AA72" s="3">
         <v>-300</v>
       </c>
       <c r="AB72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC72" s="3">
         <v>700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1800</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-500</v>
       </c>
       <c r="AE72" s="3">
         <v>-500</v>
       </c>
       <c r="AF72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="AG72" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,92 +6766,95 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E76" s="3">
         <v>9800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>100</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
       <c r="O76" s="3">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3">
         <v>400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>400</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
       <c r="S76" s="3">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3">
         <v>-200</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
       <c r="U76" s="3">
+        <v>0</v>
+      </c>
+      <c r="V76" s="3">
         <v>200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2300</v>
       </c>
-      <c r="AD76" s="3">
-        <v>0</v>
-      </c>
       <c r="AE76" s="3">
         <v>0</v>
       </c>
@@ -6676,10 +6862,13 @@
         <v>0</v>
       </c>
       <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,108 +6962,114 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6882,94 +7077,97 @@
         <v>-800</v>
       </c>
       <c r="E81" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F81" s="3">
         <v>-700</v>
       </c>
       <c r="G81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-800</v>
       </c>
       <c r="J81" s="3">
         <v>-800</v>
       </c>
       <c r="K81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>300</v>
       </c>
       <c r="R81" s="3">
         <v>300</v>
       </c>
       <c r="S81" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="T81" s="3">
         <v>-200</v>
       </c>
       <c r="U81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V81" s="3">
         <v>-1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
       <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2300</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,19 +7787,22 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-100</v>
       </c>
       <c r="G89" s="3">
         <v>-100</v>
@@ -7603,11 +7820,11 @@
         <v>-100</v>
       </c>
       <c r="L89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
@@ -7651,11 +7868,11 @@
         <v>0</v>
       </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
         <v>0</v>
       </c>
@@ -7663,13 +7880,16 @@
         <v>0</v>
       </c>
       <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7774,20 +7995,20 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB91" s="3">
-        <v>-100</v>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
+      <c r="AD91" s="3">
+        <v>-100</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8012,17 +8242,17 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -8033,17 +8263,17 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -8051,11 +8281,11 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>500</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8065,14 +8295,14 @@
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB94" s="3">
-        <v>-100</v>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
+      <c r="AD94" s="3">
+        <v>-100</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>4</v>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,29 +8741,32 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -8528,11 +8774,11 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8542,17 +8788,17 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -8576,13 +8822,13 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC100" s="3">
         <v>100</v>
       </c>
       <c r="AD100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -8591,18 +8837,21 @@
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -8646,8 +8895,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>4</v>
@@ -8664,8 +8913,8 @@
       <c r="Y101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -8688,44 +8937,47 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9200</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
       </c>
       <c r="H102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
@@ -8733,29 +8985,29 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>400</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
@@ -8778,9 +9030,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NGLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NGLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>NGLD</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,22 +1138,23 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
+      <c r="G12" s="3">
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
@@ -1148,23 +1162,23 @@
       <c r="I12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N12" s="3">
         <v>0</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
+      <c r="O12" s="3">
+        <v>0</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
@@ -1172,17 +1186,17 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>4</v>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U12" s="3">
-        <v>0</v>
+      <c r="U12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V12" s="3">
         <v>0</v>
@@ -1194,23 +1208,23 @@
         <v>0</v>
       </c>
       <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>4</v>
+      <c r="AA12" s="3">
+        <v>0</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3">
-        <v>0</v>
-      </c>
       <c r="AE12" s="3">
         <v>0</v>
       </c>
@@ -1221,10 +1235,13 @@
         <v>0</v>
       </c>
       <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,43 +1576,44 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>700</v>
       </c>
       <c r="G17" s="3">
         <v>700</v>
       </c>
       <c r="H17" s="3">
+        <v>700</v>
+      </c>
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>400</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
       </c>
       <c r="L17" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="M17" s="3">
         <v>100</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17" s="3">
         <v>0</v>
@@ -1607,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="U17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V17" s="3">
         <v>100</v>
@@ -1619,11 +1646,11 @@
         <v>100</v>
       </c>
       <c r="Y17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
       <c r="AA17" s="3">
         <v>0</v>
       </c>
@@ -1631,11 +1658,11 @@
         <v>0</v>
       </c>
       <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3">
         <v>700</v>
       </c>
-      <c r="AD17" s="3">
-        <v>0</v>
-      </c>
       <c r="AE17" s="3">
         <v>0</v>
       </c>
@@ -1643,13 +1670,16 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,34 +1687,34 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-700</v>
       </c>
       <c r="G18" s="3">
         <v>-700</v>
       </c>
       <c r="H18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-400</v>
       </c>
       <c r="K18" s="3">
         <v>-400</v>
       </c>
       <c r="L18" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="M18" s="3">
         <v>-100</v>
       </c>
       <c r="N18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
@@ -1705,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
         <v>-100</v>
@@ -1717,11 +1747,11 @@
         <v>-100</v>
       </c>
       <c r="Y18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
         <v>0</v>
       </c>
@@ -1729,11 +1759,11 @@
         <v>0</v>
       </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
       <c r="AE18" s="3">
         <v>0</v>
       </c>
@@ -1741,13 +1771,16 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,85 +1825,85 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-400</v>
       </c>
       <c r="K20" s="3">
         <v>-400</v>
       </c>
       <c r="L20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
       </c>
       <c r="S20" s="3">
         <v>300</v>
       </c>
       <c r="T20" s="3">
+        <v>300</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>2300</v>
       </c>
       <c r="AD20" s="3">
         <v>2300</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
@@ -1880,8 +1914,11 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1897,12 +1934,12 @@
       <c r="G21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3">
         <v>-500</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1978,43 +2015,46 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
@@ -2031,8 +2071,8 @@
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -2052,14 +2092,14 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2076,106 +2116,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E23" s="3">
         <v>-800</v>
       </c>
       <c r="F23" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G23" s="3">
         <v>-700</v>
       </c>
       <c r="H23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-800</v>
       </c>
       <c r="K23" s="3">
         <v>-800</v>
       </c>
       <c r="L23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>300</v>
       </c>
       <c r="S23" s="3">
         <v>300</v>
       </c>
       <c r="T23" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="U23" s="3">
         <v>-200</v>
       </c>
       <c r="V23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W23" s="3">
         <v>-1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
       <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2300</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
         <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2255,11 +2301,11 @@
         <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E26" s="3">
         <v>-800</v>
       </c>
       <c r="F26" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G26" s="3">
         <v>-700</v>
       </c>
       <c r="H26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-800</v>
       </c>
       <c r="K26" s="3">
         <v>-800</v>
       </c>
       <c r="L26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
-      </c>
-      <c r="R26" s="3">
-        <v>300</v>
       </c>
       <c r="S26" s="3">
         <v>300</v>
       </c>
       <c r="T26" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="U26" s="3">
         <v>-200</v>
       </c>
       <c r="V26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W26" s="3">
         <v>-1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2300</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
         <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
         <v>-800</v>
       </c>
       <c r="F27" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G27" s="3">
         <v>-700</v>
       </c>
       <c r="H27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-800</v>
       </c>
       <c r="K27" s="3">
         <v>-800</v>
       </c>
       <c r="L27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>300</v>
       </c>
       <c r="S27" s="3">
         <v>300</v>
       </c>
       <c r="T27" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="U27" s="3">
         <v>-200</v>
       </c>
       <c r="V27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W27" s="3">
         <v>-1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2300</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
         <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,85 +3037,85 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>400</v>
       </c>
       <c r="K32" s="3">
         <v>400</v>
       </c>
       <c r="L32" s="3">
+        <v>400</v>
+      </c>
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
       </c>
       <c r="S32" s="3">
         <v>-300</v>
       </c>
       <c r="T32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>400</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-2300</v>
       </c>
       <c r="AD32" s="3">
         <v>-2300</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E33" s="3">
         <v>-800</v>
       </c>
       <c r="F33" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G33" s="3">
         <v>-700</v>
       </c>
       <c r="H33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-800</v>
       </c>
       <c r="K33" s="3">
         <v>-800</v>
       </c>
       <c r="L33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>300</v>
       </c>
       <c r="S33" s="3">
         <v>300</v>
       </c>
       <c r="T33" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="U33" s="3">
         <v>-200</v>
       </c>
       <c r="V33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W33" s="3">
         <v>-1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2300</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
         <v>0</v>
       </c>
       <c r="AG33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E35" s="3">
         <v>-800</v>
       </c>
       <c r="F35" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G35" s="3">
         <v>-700</v>
       </c>
       <c r="H35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-800</v>
       </c>
       <c r="K35" s="3">
         <v>-800</v>
       </c>
       <c r="L35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>300</v>
       </c>
       <c r="S35" s="3">
         <v>300</v>
       </c>
       <c r="T35" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="U35" s="3">
         <v>-200</v>
       </c>
       <c r="V35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W35" s="3">
         <v>-1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2300</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
         <v>0</v>
       </c>
       <c r="AG35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,34 +3611,35 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E41" s="3">
         <v>9600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1400</v>
       </c>
       <c r="L41" s="3">
         <v>1400</v>
@@ -3561,10 +3648,10 @@
         <v>1400</v>
       </c>
       <c r="N41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O41" s="3">
         <v>1000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>900</v>
       </c>
       <c r="P41" s="3">
         <v>900</v>
@@ -3576,13 +3663,13 @@
         <v>900</v>
       </c>
       <c r="S41" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="T41" s="3">
         <v>500</v>
       </c>
       <c r="U41" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V41" s="3">
         <v>400</v>
@@ -3594,7 +3681,7 @@
         <v>400</v>
       </c>
       <c r="Y41" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Z41" s="3">
         <v>0</v>
@@ -3618,13 +3705,16 @@
         <v>0</v>
       </c>
       <c r="AG41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,22 +4013,25 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>500</v>
       </c>
       <c r="F45" s="3">
         <v>500</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -3941,11 +4040,11 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4015,46 +4114,49 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E46" s="3">
         <v>10100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1500</v>
-      </c>
-      <c r="L46" s="3">
-        <v>1400</v>
       </c>
       <c r="M46" s="3">
         <v>1400</v>
       </c>
       <c r="N46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O46" s="3">
         <v>1000</v>
-      </c>
-      <c r="O46" s="3">
-        <v>900</v>
       </c>
       <c r="P46" s="3">
         <v>900</v>
@@ -4066,26 +4168,26 @@
         <v>900</v>
       </c>
       <c r="S46" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="T46" s="3">
         <v>500</v>
       </c>
       <c r="U46" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V46" s="3">
         <v>400</v>
       </c>
       <c r="W46" s="3">
+        <v>400</v>
+      </c>
+      <c r="X46" s="3">
         <v>500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="Y46" s="3">
-        <v>0</v>
-      </c>
       <c r="Z46" s="3">
         <v>0</v>
       </c>
@@ -4108,21 +4210,24 @@
         <v>0</v>
       </c>
       <c r="AG46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E47" s="3">
         <v>900</v>
-      </c>
-      <c r="E47" s="3">
-        <v>800</v>
       </c>
       <c r="F47" s="3">
         <v>800</v>
@@ -4134,73 +4239,73 @@
         <v>800</v>
       </c>
       <c r="I47" s="3">
+        <v>800</v>
+      </c>
+      <c r="J47" s="3">
         <v>900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>800</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>1000</v>
       </c>
       <c r="AB47" s="3">
         <v>1000</v>
       </c>
       <c r="AC47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD47" s="3">
         <v>1400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2400</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>100</v>
       </c>
       <c r="AF47" s="3">
         <v>100</v>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,8 +4922,11 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4808,85 +4934,85 @@
         <v>11000</v>
       </c>
       <c r="E54" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F54" s="3">
         <v>11100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2000</v>
-      </c>
-      <c r="N54" s="3">
-        <v>1500</v>
       </c>
       <c r="O54" s="3">
         <v>1500</v>
       </c>
       <c r="P54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q54" s="3">
         <v>1800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2400</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>100</v>
       </c>
       <c r="AF54" s="3">
         <v>100</v>
@@ -4895,10 +5021,13 @@
         <v>100</v>
       </c>
       <c r="AH54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5002,7 +5133,7 @@
         <v>800</v>
       </c>
       <c r="M57" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="N57" s="3">
         <v>400</v>
@@ -5017,19 +5148,19 @@
         <v>400</v>
       </c>
       <c r="R57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
       </c>
       <c r="T57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U57" s="3">
         <v>400</v>
       </c>
       <c r="V57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W57" s="3">
         <v>300</v>
@@ -5041,20 +5172,20 @@
         <v>300</v>
       </c>
       <c r="Z57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA57" s="3">
         <v>200</v>
       </c>
       <c r="AB57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC57" s="3">
         <v>100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
       <c r="AE57" s="3">
         <v>0</v>
       </c>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5087,24 +5221,24 @@
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5121,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>1100</v>
       </c>
       <c r="V58" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="W58" s="3">
         <v>1000</v>
       </c>
       <c r="X58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>800</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>600</v>
       </c>
       <c r="AA58" s="3">
         <v>600</v>
@@ -5151,10 +5285,10 @@
         <v>600</v>
       </c>
       <c r="AD58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE58" s="3">
         <v>200</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>100</v>
       </c>
       <c r="AF58" s="3">
         <v>100</v>
@@ -5165,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5198,10 +5335,10 @@
         <v>500</v>
       </c>
       <c r="M59" s="3">
+        <v>500</v>
+      </c>
+      <c r="N59" s="3">
         <v>1000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1100</v>
       </c>
       <c r="O59" s="3">
         <v>1100</v>
@@ -5219,7 +5356,7 @@
         <v>1100</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5287,25 +5427,25 @@
         <v>1300</v>
       </c>
       <c r="J60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1500</v>
       </c>
       <c r="O60" s="3">
         <v>1500</v>
       </c>
       <c r="P60" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="Q60" s="3">
         <v>1400</v>
@@ -5326,16 +5466,16 @@
         <v>1400</v>
       </c>
       <c r="W60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X60" s="3">
         <v>1300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>800</v>
       </c>
       <c r="AA60" s="3">
         <v>800</v>
@@ -5347,10 +5487,10 @@
         <v>800</v>
       </c>
       <c r="AD60" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE60" s="3">
         <v>200</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>100</v>
       </c>
       <c r="AF60" s="3">
         <v>100</v>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5542,8 +5688,8 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
+      <c r="AD62" s="3">
+        <v>0</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,8 +6006,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5875,25 +6033,25 @@
         <v>1300</v>
       </c>
       <c r="J66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K66" s="3">
         <v>2400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1800</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1500</v>
       </c>
       <c r="O66" s="3">
         <v>1500</v>
       </c>
       <c r="P66" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="Q66" s="3">
         <v>1400</v>
@@ -5914,16 +6072,16 @@
         <v>1400</v>
       </c>
       <c r="W66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X66" s="3">
         <v>1300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>800</v>
       </c>
       <c r="AA66" s="3">
         <v>800</v>
@@ -5935,10 +6093,10 @@
         <v>800</v>
       </c>
       <c r="AD66" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE66" s="3">
         <v>200</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>100</v>
       </c>
       <c r="AF66" s="3">
         <v>100</v>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>-300</v>
       </c>
       <c r="AB72" s="3">
         <v>-300</v>
       </c>
       <c r="AC72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD72" s="3">
         <v>700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1800</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>-500</v>
       </c>
       <c r="AF72" s="3">
         <v>-500</v>
       </c>
       <c r="AG72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="AH72" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,8 +6952,11 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6778,86 +6964,86 @@
         <v>9700</v>
       </c>
       <c r="E76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F76" s="3">
         <v>9800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>100</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
       <c r="P76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3">
         <v>400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>400</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
+        <v>0</v>
+      </c>
+      <c r="U76" s="3">
         <v>-200</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
       <c r="V76" s="3">
+        <v>0</v>
+      </c>
+      <c r="W76" s="3">
         <v>200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2300</v>
       </c>
-      <c r="AE76" s="3">
-        <v>0</v>
-      </c>
       <c r="AF76" s="3">
         <v>0</v>
       </c>
@@ -6865,10 +7051,13 @@
         <v>0</v>
       </c>
       <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E81" s="3">
         <v>-800</v>
       </c>
       <c r="F81" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G81" s="3">
         <v>-700</v>
       </c>
       <c r="H81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-800</v>
       </c>
       <c r="K81" s="3">
         <v>-800</v>
       </c>
       <c r="L81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>300</v>
       </c>
       <c r="S81" s="3">
         <v>300</v>
       </c>
       <c r="T81" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="U81" s="3">
         <v>-200</v>
       </c>
       <c r="V81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W81" s="3">
         <v>-1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2300</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
         <v>0</v>
       </c>
       <c r="AG81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,22 +8004,25 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-100</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
@@ -7823,11 +8040,11 @@
         <v>-100</v>
       </c>
       <c r="M89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
@@ -7871,11 +8088,11 @@
         <v>0</v>
       </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
         <v>0</v>
       </c>
@@ -7883,13 +8100,16 @@
         <v>0</v>
       </c>
       <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7998,20 +8219,20 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
-        <v>-100</v>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
+      <c r="AE91" s="3">
+        <v>-100</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>4</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,13 +8445,16 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -8245,17 +8475,17 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -8266,17 +8496,17 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -8284,11 +8514,11 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>500</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8298,14 +8528,14 @@
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
-        <v>-100</v>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
+      <c r="AE94" s="3">
+        <v>-100</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,32 +8987,35 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9600</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -8777,11 +9023,11 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8791,17 +9037,17 @@
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8825,13 +9071,13 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="3">
         <v>100</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
@@ -8840,10 +9086,13 @@
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8853,8 +9102,8 @@
       <c r="E101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -8898,8 +9147,8 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>4</v>
@@ -8916,8 +9165,8 @@
       <c r="Z101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8940,47 +9189,50 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
@@ -8988,29 +9240,29 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
@@ -9033,9 +9285,12 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-300</v>
       </c>
     </row>
